--- a/docs/StructureDefinition-BRConjuntoMinimoDados-1.1.xlsx
+++ b/docs/StructureDefinition-BRConjuntoMinimoDados-1.1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -377,7 +377,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1056,7 +1056,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1134,7 +1134,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1207,7 +1207,7 @@
     <t>Composition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Composition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1523,7 +1523,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1747,7 +1747,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1830,13 +1830,13 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1922,7 +1922,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1968,7 +1968,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -2775,7 +2775,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>171</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>194</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>243</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>254</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>263</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>275</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>287</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>304</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>311</v>
       </c>
@@ -11080,7 +11080,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>406</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>417</v>
       </c>
@@ -12956,7 +12956,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>442</v>
       </c>
@@ -17997,7 +17997,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>640</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
         <v>654</v>
       </c>
@@ -20345,7 +20345,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>670</v>
       </c>
@@ -21640,7 +21640,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>683</v>
       </c>
@@ -21989,7 +21989,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>687</v>
       </c>
@@ -22457,7 +22457,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>691</v>
       </c>
@@ -23984,7 +23984,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
         <v>716</v>
       </c>
@@ -25279,7 +25279,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="194" hidden="true">
+    <row r="194">
       <c r="A194" t="s" s="2">
         <v>729</v>
       </c>
@@ -26334,12 +26334,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO202">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
